--- a/ftse100_buffett_value_analysis.xlsx
+++ b/ftse100_buffett_value_analysis.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,8 +85,14 @@
       <color rgb="00721C24"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00856404"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +115,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
         <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -170,6 +182,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -542,7 +557,7 @@
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
@@ -591,7 +606,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -601,7 +616,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +626,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +636,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -631,7 +646,7 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11"/>
@@ -688,12 +703,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>ABDN.L</t>
+          <t>PRU.L</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>ABERDEEN GROUP PLC ORD 13 61/63</t>
+          <t>PRUDENTIAL PLC ORD 5P</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -702,7 +717,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -710,149 +725,149 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>70</v>
+        <v>62.4</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2.46</v>
+        <v>9.58</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>8.210000000000001</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>AAF.L</t>
+          <t>ICG.L</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>AIRTEL AFRICA PLC ORD USD0.50</t>
+          <t>ICG PLC ORD 26 1/4P</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>70</v>
+        <v>59.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>3.05</v>
+        <v>19.08</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>10.17</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>ADM.L</t>
+          <t>FRES.L</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>ADMIRAL GROUP PLC ORD 0.1P</t>
+          <t>FRESNILLO PLC ORD USD0.50</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>-100</v>
+        <v>60.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>38.32</v>
+        <v>29.94</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>75.43000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>III.L</t>
+          <t>SDR.L</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>3I GROUP PLC ORD 73 19/22P</t>
+          <t>SCHRODERS PLC ORD 20P</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>-100</v>
+        <v>46.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>27.14</v>
+        <v>5.89</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>ALW.L</t>
+          <t>EDV.L</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>ALLIANCE WITAN PLC ORD 2.5P</t>
+          <t>ENDEAVOUR MINING PLC ORD USD0.0</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>-100</v>
+        <v>57.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>13.58</v>
+        <v>47.2</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>111.16</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -984,12 +999,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>ABDN.L</t>
+          <t>PRU.L</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>ABERDEEN GROUP PLC ORD 13 61/63</t>
+          <t>PRUDENTIAL PLC ORD 5P</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -1003,301 +1018,6381 @@
         </is>
       </c>
       <c r="E2" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2.46</v>
+        <v>9.58</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>8.210000000000001</v>
+        <v>25.46</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>70</v>
+        <v>62.4</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>11.73</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>0.88</v>
+        <v>1.63</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>1.18</v>
+        <v>2.45</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>7.6</v>
+        <v>18.74</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>28.07</v>
+        <v>25.49</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>238.91</v>
+        <v>1.52</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>21.93</v>
+        <v>17.49</v>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>6.09</v>
+        <v>2.1</v>
       </c>
       <c r="R2" s="5" t="n">
-        <v>69.86</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>AAF.L</t>
+          <t>ICG.L</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>AIRTEL AFRICA PLC ORD USD0.50</t>
+          <t>ICG PLC ORD 26 1/4P</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="E3" s="12" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>3.05</v>
+        <v>19.08</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>10.17</v>
+        <v>46.67</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>70</v>
+        <v>59.1</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>21.76</v>
+        <v>11.63</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>4.66</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5" t="n">
         <v/>
       </c>
       <c r="L3" s="5" t="n">
-        <v>26.41</v>
+        <v>18.44</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>10.37</v>
+        <v>48.94</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>1.84</v>
+        <v>0.47</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>12.01</v>
+        <v>15.26</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>1.68</v>
+        <v>4.57</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>36.66</v>
+        <v>51.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>ADM.L</t>
+          <t>FRES.L</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ADMIRAL GROUP PLC ORD 0.1P</t>
+          <t>FRESNILLO PLC ORD USD0.50</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>SELL</t>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="E4" s="12" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>38.32</v>
+        <v>29.94</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-100</v>
+        <v>60.3</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>17.58</v>
+        <v>12.96</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>7.72</v>
+        <v>5.75</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>45.56</v>
+        <v>52.98</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>13.36</v>
+        <v>37.95</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>1.39</v>
+        <v>0.15</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>6.13</v>
+        <v>6.35</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-38.76</v>
+        <v>9.06</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>72.87</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>III.L</t>
+          <t>SDR.L</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3I GROUP PLC ORD 73 19/22P</t>
+          <t>SCHRODERS PLC ORD 20P</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>SELL</t>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>27.14</v>
+        <v>5.89</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>11.05</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-100</v>
+        <v>46.7</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>5.04</v>
+        <v>13.7</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.89</v>
+        <v>2.07</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v/>
+        <v>1.28</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v/>
+        <v>15.76</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v/>
+        <v>19.12</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v/>
+        <v>0.13</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v/>
+        <v>4.58</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v/>
+        <v>6.75</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v/>
+        <v>3.74</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v/>
+        <v>49.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>EDV.L</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ENDEAVOUR MINING PLC ORD USD0.0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>111.16</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>42.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ABDN.L</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ABERDEEN GROUP PLC ORD 13 61/63</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>238.91</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>69.86</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>HSX.L</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>HISCOX LTD ORD 6.5P (DI)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>82.67</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>III.L</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>3I GROUP PLC ORD 73 19/22P</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>14.67</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>SHEL.L</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>SHELL PLC ORD EUR0.07</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>104.43</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>32.82</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>AUTO.L</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>AUTOTRADER GROUP PLC ORD 1P</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>STJ.L</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>ST. JAMES'S PLACE PLC ORD 15P</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>16.89</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>IGG.L</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>IG GROUP HOLDINGS PLC ORD 0.005</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>44.24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>CNA.L</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>CENTRICA PLC ORD 6 14/81P</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>36.42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>SN.L</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SMITH &amp; NEPHEW PLC ORD USD0.20</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>52.45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>JD.L</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>JD SPORTS FASHION PLC ORD 0.05P</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>11.71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>LAND.L</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>LAND SECURITIES GROUP PLC ORD 1</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>68.19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>PSON.L</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>PEARSON PLC ORD 25P</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>RKT.L</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>RECKITT BENCKISER GROUP PLC ORD</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>74.11</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>48.63</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>CCH.L</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>COCA-COLA HBC AG ORD CHF6.70 (C</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>44.08</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>25.96</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>43.96</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>RIO.L</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>RIO TINTO PLC ORD 10P</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>79.66</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>54.88</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>BNZL.L</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>BUNZL PLC ORD 32 1/7P</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>49.07</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>IMB.L</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>IMPERIAL BRANDS PLC ORD 10P</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>75.41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>REL.L</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>RELX PLC ORD 14 51/116P</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>35.69</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>131.86</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>54.09</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>VOD.L</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VODAFONE GROUP PLC ORD USD0.20 </t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>101.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>KGF.L</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>KINGFISHER PLC ORD 15 5/7P</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>89.86</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>MTLN.L</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">METLEN ENERGY &amp; METALS PLC ORD </t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>142.95</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="Q27" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>38.37</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>AAF.L</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>AIRTEL AFRICA PLC ORD USD0.50</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>36.66</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>ITH.L</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>ITHACA ENERGY PLC ORD 1P</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>191.41</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>LGEN.L</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>LEGAL &amp; GENERAL GROUP PLC ORD 2</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>189.97</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>DCC.L</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>DCC ENERGY PLC ORD EUR0.25 (CDI</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>425.82</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>72.88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>BP.L</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>BP PLC $0.25</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>95.56</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>LLOY.L</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>LLOYDS BANKING GROUP PLC ORD 10</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>45.63</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>SGE.L</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>THE SAGE GROUP PLC ORD 1 4/77P</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>75.56</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>55.02</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>AAL.L</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>ANGLO AMERICAN PLC ORD USD0.623</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>-13.94</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>561.02</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>MNG.L</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>M&amp;G PLC</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>164.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>RTO.L</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>RENTOKIL INITIAL PLC ORD 1P</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>97.53</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>BTRW.L</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>BARRATT REDROW PLC ORD 10P</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>101.79</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>NXT.L</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>NEXT PLC ORD 10P</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>178.84</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>34.09</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>CCC.L</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>COMPUTACENTER PLC ORD 7 5/9P</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>38.51</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>SBRY.L</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>SAINSBURY (J) PLC ORD 28 4/7P</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>77.53</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>BT-A.L</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>BT GROUP PLC ORD 5P</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>76.02</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>BRBY.L</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>BURBERRY GROUP PLC ORD 0.05P</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>170.67</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>TSCO.L</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>TESCO PLC ORD 6 1/3P</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>52.58</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>IMI.L</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>IMI PLC ORD 28 4/7P</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>37.24</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>GLEN.L</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>GLENCORE PLC ORD USD0.01</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>30.03</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>HWDN.L</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>HOWDEN JOINERY GROUP PLC ORD 10</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="Q47" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>44.88</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>BLND.L</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>BRITISH LAND COMPANY PLC ORD 25</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>50.51</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>LSEG.L</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>LONDON STOCK EXCHANGE GROUP PLC</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>81.54000000000001</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>99.14</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>29.33</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="Q49" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R49" s="5" t="n">
+        <v>53.94</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>HLN.L</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>HALEON PLC ORD GBP0.01</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>39.23</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>INF.L</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>INFORMA PLC ORD 0.1P</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>52.81</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P51" s="5" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="Q51" s="5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R51" s="5" t="n">
+        <v>128.65</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>GAW.L</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>GAMES WORKSHOP GROUP PLC ORD 5P</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>-120.9</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>66.87</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>77.91</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>EXPN.L</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>EXPERIAN PLC ORD USD0.10</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P53" s="5" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="Q53" s="5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R53" s="5" t="n">
+        <v>39.78</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>SDLF.L</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>STANDARD LIFE PLC ORD 10P</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>1081.45</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>-43.04</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>-31.89</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>416.56</v>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>51.15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>ULVR.L</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>UNILEVER PLC ORD 3.5P</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P55" s="5" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="Q55" s="5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R55" s="5" t="n">
+        <v>76.11</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>NWG.L</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>NATWEST GROUP PLC ORD 107.69P</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P56" s="5" t="n">
+        <v>-22.37</v>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="R56" s="5" t="n">
+        <v>43.57</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>BATS.L</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>BRITISH AMERICAN TOBACCO PLC OR</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>-67.40000000000001</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P57" s="5" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="Q57" s="5" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="R57" s="5" t="n">
+        <v>83.44</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>BEZ.L</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>BEAZLEY PLC ORD 5P</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R58" s="5" t="n">
+        <v>30.04</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>BARC.L</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>BARCLAYS PLC ORD 25P</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P59" s="5" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="Q59" s="5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R59" s="5" t="n">
+        <v>17.81</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>ABF.L</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>ASSOCIATED BRITISH FOODS PLC OR</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P60" s="5" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="Q60" s="5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R60" s="5" t="n">
+        <v>47.27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>CCEP.L</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COCA-COLA EUROPACIFIC PARTNERS </t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>92.69</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="M61" s="5" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="N61" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O61" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P61" s="5" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="Q61" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R61" s="5" t="n">
+        <v>46.62</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>ANTO.L</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>ANTOFAGASTA PLC ORD 5P</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>-137.2</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P62" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q62" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R62" s="5" t="n">
+        <v>38.47</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>BA.L</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>BAE SYSTEMS PLC ORD 2.5P</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="N63" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O63" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P63" s="5" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="Q63" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R63" s="5" t="n">
+        <v>52.01</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>LMP.L</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>LONDONMETRIC PROPERTY PLC ORD 1</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>-55.8</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>63.01</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="R64" s="5" t="n">
+        <v>95.77</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>MRO.L</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>MELROSE INDUSTRIES PLC ORD GBP0</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M65" s="5" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="N65" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O65" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P65" s="5" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="Q65" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R65" s="5" t="n">
+        <v>56.25</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>DGE.L</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>DIAGEO PLC ORD 28 101/108P</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P66" s="5" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="Q66" s="5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R66" s="5" t="n">
+        <v>106.6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>UU.L</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNITED UTILITIES GROUP PLC ORD </t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="M67" s="5" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="N67" s="5" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="O67" s="5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P67" s="5" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="Q67" s="5" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R67" s="5" t="n">
+        <v>61.13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>HLMA.L</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>HALMA PLC ORD 10P</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>-86.3</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="N68" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q68" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="R68" s="5" t="n">
+        <v>24.19</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>HSBA.L</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>HSBC HOLDINGS PLC ORD $0.50 (UK</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="N69" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O69" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P69" s="5" t="n">
+        <v>-27.32</v>
+      </c>
+      <c r="Q69" s="5" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="R69" s="5" t="n">
+        <v>52.64</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>STAN.L</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>STANDARD CHARTERED PLC ORD USD0</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="N70" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O70" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P70" s="5" t="n">
+        <v>-71.3</v>
+      </c>
+      <c r="Q70" s="5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R70" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>INVP.L</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>INVESTEC PLC ORD GBP0.0002</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="N71" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O71" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P71" s="5" t="n">
+        <v>-70.59999999999999</v>
+      </c>
+      <c r="Q71" s="5" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="R71" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>GSK.L</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>GSK PLC ORD 31 1/4P</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>-44.3</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P72" s="5" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="R72" s="5" t="n">
+        <v>56.88</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>IAG.L</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL CONSOLIDATED AIRL</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="N73" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O73" s="5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P73" s="5" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="Q73" s="5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R73" s="5" t="n">
+        <v>15.26</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>BGEO.L</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>LION FINANCE GROUP PLC ORD 1P</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="N74" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O74" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P74" s="5" t="n">
+        <v/>
+      </c>
+      <c r="Q74" s="5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R74" s="5" t="n">
+        <v>24.86</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>DPLM.L</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>DIPLOMA PLC ORD 5P</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>-128.3</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N75" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="O75" s="5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="P75" s="5" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q75" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R75" s="5" t="n">
+        <v>44.25</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>SGRO.L</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>SEGRO PLC ORD 10P</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>-117.7</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="N76" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O76" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P76" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q76" s="5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R76" s="5" t="n">
+        <v>73.45999999999999</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>SPX.L</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>SPIRAX GROUP PLC ORD 26 12/13P</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>-18.7</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="N77" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="O77" s="5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P77" s="5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q77" s="5" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="R77" s="5" t="n">
+        <v>63.34</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>AZN.L</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>ASTRAZENECA PLC ORD SHS $0.25</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>126.72</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>-154.1</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P78" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R78" s="5" t="n">
+        <v>47.41</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>RR.L</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>ROLLS-ROYCE HOLDINGS PLC ORD SH</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>-74.59999999999999</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>114.48</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="N79" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O79" s="5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P79" s="5" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="Q79" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R79" s="5" t="n">
+        <v>26.19</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>SSE.L</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>SSE PLC ORD 50P</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="N80" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O80" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P80" s="5" t="n">
+        <v>-7.58</v>
+      </c>
+      <c r="Q80" s="5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="R80" s="5" t="n">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>NG.L</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>NATIONAL GRID PLC ORD 12 204/47</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="N81" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="O81" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P81" s="5" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="Q81" s="5" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R81" s="5" t="n">
+        <v>72.11</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>ADM.L</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>ADMIRAL GROUP PLC ORD 0.1P</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="N82" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O82" s="5" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="P82" s="5" t="n">
+        <v>-40.08</v>
+      </c>
+      <c r="Q82" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R82" s="5" t="n">
+        <v>72.87</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>WEIR.L</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>WEIR PLC ORD 12.5P</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>-104.2</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="N83" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O83" s="5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P83" s="5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q83" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R83" s="5" t="n">
+        <v>40.96</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>ITRK.L</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>INTERTEK GROUP PLC ORD 1P</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>-29.7</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>29.94</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="N84" s="5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O84" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P84" s="5" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="Q84" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R84" s="5" t="n">
+        <v>80.45</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>PSH.L</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>PERSHING SQUARE HOLDINGS LTD OR</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="O85" s="5" t="n">
+        <v>155.54</v>
+      </c>
+      <c r="P85" s="5" t="n">
+        <v>-13.81</v>
+      </c>
+      <c r="Q85" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R85" s="5" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>CPG.L</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>COMPASS GROUP PLC ORD 11 1/20P</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="N86" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O86" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P86" s="5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Q86" s="5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R86" s="5" t="n">
+        <v>55.92</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>CRDA.L</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>CRODA INTERNATIONAL PLC ORD 10.</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>-105.8</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="N87" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O87" s="5" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P87" s="5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q87" s="5" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R87" s="5" t="n">
+        <v>195.08</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>SMIN.L</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>SMITHS GROUP PLC ORD 37.5P</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="N88" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O88" s="5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P88" s="5" t="n">
+        <v>-9.92</v>
+      </c>
+      <c r="Q88" s="5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R88" s="5" t="n">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>EZJ.L</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>EASYJET PLC ORD 27 2/7P</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="N89" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="O89" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P89" s="5" t="n">
+        <v>-16.19</v>
+      </c>
+      <c r="Q89" s="5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R89" s="5" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>SVT.L</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>SEVERN TRENT PLC ORD 97 17/19P</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N90" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="O90" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P90" s="5" t="n">
+        <v>-12.46</v>
+      </c>
+      <c r="Q90" s="5" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="R90" s="5" t="n">
+        <v>100.27</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>IHG.L</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>INTERCONTINENTAL HOTELS GROUP P</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>154.1</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>94.92</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>-62.3</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>-7.76</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N91" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O91" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P91" s="5" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="Q91" s="5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R91" s="5" t="n">
+        <v>39.14</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>CTEC.L</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>CONVATEC GROUP PLC ORD 10P</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="N92" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O92" s="5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P92" s="5" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="Q92" s="5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R92" s="5" t="n">
+        <v>116.9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>WTB.L</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>WHITBREAD PLC ORD 76 122/153P</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>-377.3</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="N93" s="5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P93" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q93" s="5" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="R93" s="5" t="n">
+        <v>79.25</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>BAB.L</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>BABCOCK INTERNATIONAL GROUP PLC</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>-68.5</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="M94" s="5" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="N94" s="5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O94" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P94" s="5" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Q94" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R94" s="5" t="n">
+        <v>16.95</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>MKS.L</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>MARKS AND SPENCER GROUP PLC ORD</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M95" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N95" s="5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O95" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P95" s="5" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="Q95" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R95" s="5" t="n">
+        <v>30.89</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>SMT.L</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>SCOTTISH MORTGAGE INVESTMENT TR</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M96" s="5" t="n">
+        <v/>
+      </c>
+      <c r="N96" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O96" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P96" s="5" t="n">
+        <v/>
+      </c>
+      <c r="Q96" s="5" t="n">
+        <v/>
+      </c>
+      <c r="R96" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>FCIT.L</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>F&amp;C INVESTMENT TRUST PLC ORD 6.</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="N97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="Q97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="R97" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>PCT.L</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POLAR CAPITAL TECHNOLOGY TRUST </t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M98" s="5" t="n">
+        <v/>
+      </c>
+      <c r="N98" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O98" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P98" s="5" t="n">
+        <v/>
+      </c>
+      <c r="Q98" s="5" t="n">
+        <v/>
+      </c>
+      <c r="R98" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>AV.L</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>AVIVA PLC ORD 32 17/19P</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="M99" s="5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="N99" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O99" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P99" s="5" t="n">
+        <v>-10.83</v>
+      </c>
+      <c r="Q99" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="R99" s="5" t="n">
+        <v>229.82</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>BBOX.L</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>TRITAX BIG BOX REIT PLC ORD 1P</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M100" s="5" t="n">
+        <v/>
+      </c>
+      <c r="N100" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O100" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P100" s="5" t="n">
+        <v/>
+      </c>
+      <c r="Q100" s="5" t="n">
+        <v/>
+      </c>
+      <c r="R100" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
           <t>ALW.L</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>ALLIANCE WITAN PLC ORD 2.5P</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D101" s="14" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E101" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="G6" s="5" t="n">
+      <c r="F101" s="5" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="G101" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H101" s="5" t="n">
         <v>-100</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>20.51</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="5" t="n">
+      <c r="I101" s="5" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v/>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M101" s="5" t="n">
+        <v/>
+      </c>
+      <c r="N101" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O101" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P101" s="5" t="n">
+        <v/>
+      </c>
+      <c r="Q101" s="5" t="n">
+        <v/>
+      </c>
+      <c r="R101" s="5" t="n">
         <v/>
       </c>
     </row>
@@ -1400,39 +7495,39 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>CTY.L</t>
+          <t>ISF.L</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>City of London Investment Trust</t>
+          <t>iShares Core FTSE 100 UCITS ETF</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Dividend Hero Investment Trust</t>
+          <t>FTSE 100 Index Benchmark</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>5.85</v>
+        <v>10.41</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.37</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v/>
+        <v>2.88</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>5.13</v>
+        <v>15.24</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1.13</v>
+        <v/>
       </c>
       <c r="I2" s="5" t="n">
-        <v/>
+        <v>0.74</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>3017.7</v>
+        <v/>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
@@ -1446,99 +7541,99 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Famous UK Investment Trust with 58+ consecutive years of dividend increases.</t>
+          <t>Direct low-cost physical index tracking of top 100 UK blue chips.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>FCIT.L</t>
+          <t>SMT.L</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>F&amp;C Investment Trust</t>
+          <t>Scottish Mortgage Investment Trust</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Global Dividend Trust</t>
+          <t>Growth &amp; Quality Trust</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>3.43</v>
+        <v>15.72</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.54</v>
+        <v>0.34</v>
       </c>
       <c r="F3" s="5" t="n">
         <v/>
       </c>
       <c r="G3" s="5" t="n">
-        <v>4.51</v>
+        <v>5.72</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="I3" s="5" t="n">
         <v/>
       </c>
       <c r="J3" s="5" t="n">
-        <v>6419.3</v>
+        <v>16646.2</v>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>HIGH (Core Value/Index Holding)</t>
+          <t>TACTICAL</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>BENCHMARK BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>World's oldest investment trust (founded 1868) with 53+ years dividend growth.</t>
+          <t>Focuses on global quality businesses and high-conviction growth.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IWVL.L</t>
+          <t>FCIT.L</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI World Value Factor ETF</t>
+          <t>F&amp;C Investment Trust</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Global Value Factor</t>
+          <t>Global Dividend Trust</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>82.58</v>
+        <v>3.46</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="F4" s="5" t="n">
         <v/>
       </c>
       <c r="G4" s="5" t="n">
-        <v>15.39</v>
+        <v>4.55</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v/>
+        <v>0.95</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>1.14</v>
+        <v/>
       </c>
       <c r="J4" s="5" t="n">
-        <v>7642.9</v>
+        <v>6472</v>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
@@ -1552,99 +7647,99 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Global equities screened for high value metrics (low P/E, P/B, FCF).</t>
+          <t>World's oldest investment trust (founded 1868) with 53+ years dividend growth.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IUKD.L</t>
+          <t>VMID.L</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>iShares UK Dividend UCITS ETF</t>
+          <t>Vanguard FTSE 250 UCITS ETF</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>UK High Dividend / Value</t>
+          <t>UK Mid-Cap Benchmark</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>10.21</v>
+        <v>0.37</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>4.59</v>
+        <v>3.1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>15.01</v>
+        <v>15.94</v>
       </c>
       <c r="H5" s="5" t="n">
         <v/>
       </c>
       <c r="I5" s="5" t="n">
-        <v>1</v>
+        <v>-98.98</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1345.8</v>
+        <v>2225.6</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>HIGH (Core Value/Index Holding)</t>
+          <t>MODERATE (Growth/Value Blend)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>BENCHMARK BUY</t>
+          <t>HOLD / SELECT BUY</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Selects the top 50 highest dividend-yielding stocks in the UK FTSE 350.</t>
+          <t>Tracks FTSE 250 mid-caps with strong UK domestic exposure.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>VUKE.L</t>
+          <t>IWVL.L</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 100 UCITS ETF</t>
+          <t>iShares Edge MSCI World Value Factor ETF</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>FTSE 100 Index Benchmark</t>
+          <t>Global Value Factor</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.47</v>
+        <v>82.69</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2.99</v>
+        <v/>
       </c>
       <c r="G6" s="5" t="n">
-        <v>16.79</v>
+        <v>15.41</v>
       </c>
       <c r="H6" s="5" t="n">
         <v/>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-98.98999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>6662.1</v>
+        <v>7642.9</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
@@ -1658,152 +7753,152 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Vanguard standard UK blue-chip index tracker.</t>
+          <t>Global equities screened for high value metrics (low P/E, P/B, FCF).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>VMID.L</t>
+          <t>VUKE.L</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF</t>
+          <t>Vanguard FTSE 100 UCITS ETF</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>UK Mid-Cap Benchmark</t>
+          <t>FTSE 100 Index Benchmark</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>15.93</v>
+        <v>16.72</v>
       </c>
       <c r="H7" s="5" t="n">
         <v/>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-98.98</v>
+        <v>-98.98999999999999</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>2225.6</v>
+        <v>6662.1</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>MODERATE (Growth/Value Blend)</t>
+          <t>HIGH (Core Value/Index Holding)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>HOLD / SELECT BUY</t>
+          <t>BENCHMARK BUY</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Tracks FTSE 250 mid-caps with strong UK domestic exposure.</t>
+          <t>Vanguard standard UK blue-chip index tracker.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>SMT.L</t>
+          <t>IUKD.L</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Scottish Mortgage Investment Trust</t>
+          <t>iShares UK Dividend UCITS ETF</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Growth &amp; Quality Trust</t>
+          <t>UK High Dividend / Value</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>15.29</v>
+        <v>10.14</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v/>
+        <v>4.59</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>5.56</v>
+        <v>14.91</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1.19</v>
+        <v/>
       </c>
       <c r="I8" s="5" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>16188.2</v>
+        <v>1345.8</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>TACTICAL</t>
+          <t>HIGH (Core Value/Index Holding)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BENCHMARK BUY</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Focuses on global quality businesses and high-conviction growth.</t>
+          <t>Selects the top 50 highest dividend-yielding stocks in the UK FTSE 350.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>ISF.L</t>
+          <t>CTY.L</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>iShares Core FTSE 100 UCITS ETF</t>
+          <t>City of London Investment Trust</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>FTSE 100 Index Benchmark</t>
+          <t>Dividend Hero Investment Trust</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>10.46</v>
+        <v>5.81</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2.88</v>
+        <v/>
       </c>
       <c r="G9" s="5" t="n">
-        <v>15.32</v>
+        <v>5.1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v/>
+        <v>1.12</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1.22</v>
+        <v/>
       </c>
       <c r="J9" s="5" t="n">
-        <v/>
+        <v>2997</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -1817,7 +7912,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Direct low-cost physical index tracking of top 100 UK blue chips.</t>
+          <t>Famous UK Investment Trust with 58+ consecutive years of dividend increases.</t>
         </is>
       </c>
     </row>
